--- a/data/trans_orig/IQ11_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ11_1-Edad-trans_orig.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9994</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26018</t>
+          <t>25625</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>14710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>34497</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41252</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65767</t>
+          <t>65520</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73660</t>
+          <t>73812</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,79%</t>
         </is>
       </c>
     </row>
@@ -4767,12 +4767,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4817,12 +4817,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,66%</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -5328,12 +5328,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>750</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -5439,12 +5439,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16619</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24177</t>
+          <t>24032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25240</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35602</t>
+          <t>35656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6631,12 +6631,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20269</t>
+          <t>20665</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>27670</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>17870</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -7344,12 +7344,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>36979</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55216</t>
+          <t>55352</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>74886</t>
+          <t>74844</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>89764</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9753,12 +9753,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9788,12 +9788,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -10410,12 +10410,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13693</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23347</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10865,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -11082,12 +11082,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>37481</t>
+          <t>37549</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>51947</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>59823</t>
+          <t>59855</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13911,7 +13911,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -13967,7 +13967,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -14533,7 +14533,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14563,12 +14563,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14578,12 +14578,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14598,12 +14598,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -14674,12 +14674,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14709,12 +14709,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>39565</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14724,12 +14724,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
